--- a/SGC-CKN/Excel/e554cad2-d0da-42ed-bf4e-dd0a3e330907_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P379_D1200_01-04-2026.xlsx
+++ b/SGC-CKN/Excel/e554cad2-d0da-42ed-bf4e-dd0a3e330907_Xã_Cần_Giờ__TP__Hồ_Chí_Minh_P379_D1200_01-04-2026.xlsx
@@ -133,11 +133,11 @@
   </si>
   <si>
     <t xml:space="preserve">19:30
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:17
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -147,7 +147,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:46
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -157,7 +157,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:00
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -167,7 +167,7 @@
   </si>
   <si>
     <t xml:space="preserve">22:45
-30/03/2026</t>
+31/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -177,7 +177,7 @@
   </si>
   <si>
     <t xml:space="preserve">00:00
-30/03/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>9</t>
@@ -187,7 +187,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:15
-30/03/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -197,7 +197,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:30
-30/03/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>11</t>
@@ -207,7 +207,7 @@
   </si>
   <si>
     <t xml:space="preserve">05:00
-30/03/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1567,16 +1567,16 @@
         <v>-64.9</v>
       </c>
       <c r="G21" s="16">
-        <v>-70.45</v>
+        <v>-75.46</v>
       </c>
       <c r="H21" s="16">
         <v>2.5</v>
       </c>
       <c r="I21" s="16">
-        <v>5.55</v>
+        <v>10.56</v>
       </c>
       <c r="J21" s="15">
-        <v>2.22</v>
+        <v>4.22</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>29</v>
@@ -2024,16 +2024,16 @@
         <v>-64.9</v>
       </c>
       <c r="F12" s="16">
-        <v>-70.45</v>
+        <v>-75.46</v>
       </c>
       <c r="G12" s="16">
         <v>2.5</v>
       </c>
       <c r="H12" s="16">
-        <v>5.55</v>
+        <v>10.56</v>
       </c>
       <c r="I12" s="15">
-        <v>2.22</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2053,16 +2053,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="39">
-        <v>-70.45</v>
+        <v>-75.46</v>
       </c>
       <c r="G13" s="39">
         <v>11.47</v>
       </c>
       <c r="H13" s="39">
-        <v>70.45</v>
+        <v>75.46</v>
       </c>
       <c r="I13" s="39">
-        <v>6.14</v>
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>
